--- a/ECHS_District_City_Mapping.xlsx
+++ b/ECHS_District_City_Mapping.xlsx
@@ -424,12 +424,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C516"/>
+  <dimension ref="A1:C473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anantapur</t>
+          <t>Dr. B.R. Ambedkar Konaseema</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Anantpur</t>
+          <t>Amalapuram</t>
         </is>
       </c>
     </row>
@@ -508,12 +508,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dr. B.R. Ambedkar Konaseema</t>
+          <t>East Godavari</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amalapuram</t>
+          <t>Rajahmundry</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rajahmundry</t>
+          <t>Rajanagaram</t>
         </is>
       </c>
     </row>
@@ -542,12 +542,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>East Godavari</t>
+          <t>Eluru</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rajanagaram</t>
+          <t>Eluru</t>
         </is>
       </c>
     </row>
@@ -559,12 +559,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eluru</t>
+          <t>Guntur</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eluru</t>
+          <t>Guntur</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Guntur</t>
+          <t>Kakinada</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Guntur</t>
+          <t>Kakinada</t>
         </is>
       </c>
     </row>
@@ -593,12 +593,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kakinada</t>
+          <t>Kurnool</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kakinada</t>
+          <t>Kurnool</t>
         </is>
       </c>
     </row>
@@ -610,12 +610,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kurnool</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kurnool</t>
+          <t>Vijayawada</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>Nandyal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vijayawada</t>
+          <t>Nandyal</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>Nellore</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vijayawada, Krishna</t>
+          <t>Nellore</t>
         </is>
       </c>
     </row>
@@ -661,12 +661,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>Parvathipuram Manyam</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vijaywada</t>
+          <t>Rajam</t>
         </is>
       </c>
     </row>
@@ -678,12 +678,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nandyal</t>
+          <t>Prakasam</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nandyal</t>
+          <t>Giddalur</t>
         </is>
       </c>
     </row>
@@ -695,12 +695,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nellore</t>
+          <t>Prakasam</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nellore</t>
+          <t>Ongole</t>
         </is>
       </c>
     </row>
@@ -712,12 +712,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Parvathipuram Manyam</t>
+          <t>Srikakulam</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rajam</t>
+          <t>Srikakulam</t>
         </is>
       </c>
     </row>
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Prakasam</t>
+          <t>Tirupati</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Giddalur</t>
+          <t>Gudur</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Prakasam</t>
+          <t>Tirupati</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ongole</t>
+          <t>Tirupati</t>
         </is>
       </c>
     </row>
@@ -763,12 +763,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Prakasam</t>
+          <t>Visakhapatnam</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ongole Prakasam</t>
+          <t>Visakhapatnam</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Srikakulam</t>
+          <t>Vizianagaram</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Srikakulam</t>
+          <t>Vizianagaram</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tirupati</t>
+          <t>YSR Kadapa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gudur, Tirupati</t>
+          <t>Kadapa</t>
         </is>
       </c>
     </row>
@@ -814,114 +814,114 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tirupati</t>
+          <t>YSR Kadapa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tirupathi</t>
+          <t>Proddatur</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tirupati</t>
+          <t>Barpeta</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tirupati</t>
+          <t>Barpeta</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Visakhapatnam</t>
+          <t>Bongaigaon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Visakhapatna</t>
+          <t>Bongaigaon</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Visakhapatnam</t>
+          <t>Cachar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Visakhapatnam</t>
+          <t>Silchar</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vizianagaram</t>
+          <t>Dhubri</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vizianagaram</t>
+          <t>Dhubri</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YSR Kadapa</t>
+          <t>Dibrugarh</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Dibrugarh</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>YSR Kadapa</t>
+          <t>Jorhat</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Proddatur</t>
+          <t>Jorhat</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Barpeta</t>
+          <t>Kamrup</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Barpeta</t>
+          <t>Guwahati</t>
         </is>
       </c>
     </row>
@@ -950,114 +950,114 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bongaigaon</t>
+          <t>Karbi Anglong</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bongiagaon</t>
+          <t>Diphu</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cachar</t>
+          <t>Begusarai</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Silchar</t>
+          <t>Begusarai</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dhubri</t>
+          <t>Bhagalpur</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dhubri</t>
+          <t>Bhagalpur</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dibrugarh</t>
+          <t>Bhojpur</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dibrugarh</t>
+          <t>Ara</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jorhat</t>
+          <t>Bhojpur</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jorhat</t>
+          <t>Bhojpur</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kamrup</t>
+          <t>Darbhanga</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Guwahati</t>
+          <t>Darbhanga</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Karbi Anglong</t>
+          <t>Muzaffarpur</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Diphu</t>
+          <t>Muzaffarpur</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Begusarai</t>
+          <t>Patna</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Begusarai</t>
+          <t>Patna</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bhagalpur</t>
+          <t>Saran</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bhagalpur</t>
+          <t>Saran</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bhojpur</t>
+          <t>Sitamarhi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ara</t>
+          <t>Sitamarhi</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bhojpur</t>
+          <t>Siwan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bhojpur</t>
+          <t>Siwan</t>
         </is>
       </c>
     </row>
@@ -1137,233 +1137,233 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Darbhanga</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Darbhanga</t>
+          <t>Hajipur</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Muzaffarpur</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Muzaffarpur</t>
+          <t>Chandigarh</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Bastar</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Jagdalpur</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Saran</t>
+          <t>Bilaspur</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saran</t>
+          <t>Bilaspur</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sitamarhi</t>
+          <t>Durg</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sitamarhi</t>
+          <t>Bhilai</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Siwan</t>
+          <t>Durg</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Siwan</t>
+          <t>Durg</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Korba</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hajipur</t>
+          <t>Korba</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Raipur</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Raipur</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bastar</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jagdalpur</t>
+          <t>New Delhi</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bilaspur</t>
+          <t>North Delhi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bilaspur</t>
+          <t>Delhi</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Durg</t>
+          <t>North Delhi</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bhilai</t>
+          <t>North Delhi</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Durg</t>
+          <t>North West Delhi</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Durg</t>
+          <t>Narela</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Korba</t>
+          <t>North West Delhi</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Korba</t>
+          <t>Rohini</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>South East Delhi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>Sarita Vihar</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>South West Delhi</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Dwarka</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>North Delhi</t>
+          <t>South West Delhi</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Najafgarh</t>
         </is>
       </c>
     </row>
@@ -1409,131 +1409,131 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>North Delhi</t>
+          <t>West Delhi</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Delhi (North)</t>
+          <t>Nangloi</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>North West Delhi</t>
+          <t>North Goa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Narela</t>
+          <t>Panaji</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>North West Delhi</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rohini</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>South East Delhi</t>
+          <t>Bhavnagar</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sarita Vihar, South Delhi</t>
+          <t>Bhavnagar</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>South West Delhi</t>
+          <t>Gandhi Nagar</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dwarka</t>
+          <t>Gandhinagar</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>South West Delhi</t>
+          <t>Kachchh</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Najafgarh</t>
+          <t>Bhuj</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>West Delhi</t>
+          <t>Rajkot</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nangloi</t>
+          <t>Rajkot</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>North Goa</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Panaji</t>
+          <t>Surat</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Vadodara</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Vadodara</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bhavnagar</t>
+          <t>Valsad</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bhavnagar</t>
+          <t>Dharampur</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gandhi Nagar</t>
+          <t>Valsad</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gandhinagar</t>
+          <t>Valsad</t>
         </is>
       </c>
     </row>
@@ -1596,114 +1596,114 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kachchh</t>
+          <t>Valsad</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bhuj</t>
+          <t>Vapi</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Rajkot</t>
+          <t>Ambala</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rajkot</t>
+          <t>Ambala</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Ambala</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Ambala Cantt</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Ambala</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Ambala City</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Valsad</t>
+          <t>Bhiwani</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dharampur</t>
+          <t>Bhiwani</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Valsad</t>
+          <t>Bhiwani</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Valsad</t>
+          <t>Tosham</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Valsad</t>
+          <t>Charkhi Dadri</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Vapi</t>
+          <t>Charkhi Dadri</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ambala</t>
+          <t>Faridabad</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ambala</t>
+          <t>Faridabad</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ambala</t>
+          <t>Faridabad</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ambala Cantt</t>
+          <t>Hodal</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ambala</t>
+          <t>Fatehabad</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ambala City</t>
+          <t>Fatehabad</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bhiwani</t>
+          <t>Fatehabad</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bhiwani</t>
+          <t>Tohana</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bhiwani</t>
+          <t>Gurgaon</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tosham Bhiwani</t>
+          <t>Gurgaon</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Charkhi Dadri</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charak Dadri</t>
+          <t>Gurugram</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Charkhi Dadri</t>
+          <t>Hisar</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charakhi-Dadri</t>
+          <t>Hansi</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Charkhi Dadri</t>
+          <t>Hisar</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Charkhi Dadri</t>
+          <t>Hisar</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Faridabad</t>
+          <t>Jhajjar</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Faridabad</t>
+          <t>Bahadurgarh</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Faridabad</t>
+          <t>Jhajjar</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hodal</t>
+          <t>Jhajjar</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fatehabad</t>
+          <t>Jind</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fatehabad</t>
+          <t>Jind</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Fatehabad</t>
+          <t>Jind</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fathebad</t>
+          <t>Narwana</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Fatehabad</t>
+          <t>Kaithal</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tohana</t>
+          <t>Kaithal</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Gurgaon</t>
+          <t>Karnal</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Gurgaon</t>
+          <t>Karnal</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Kurukshetra</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Kurukshetra</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Hisar</t>
+          <t>Kurukshetra</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>125001</t>
+          <t>Pehowa</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Hisar</t>
+          <t>Kurukshetra</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hansi</t>
+          <t>Shahabad Markanda</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Hisar</t>
+          <t>Mahendragarh</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hisar</t>
+          <t>Mahendragarh</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hisar</t>
+          <t>Mahendragarh</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hissar</t>
+          <t>Narnaul</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Hisar</t>
+          <t>Palwal</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sirsa Road, Hisar</t>
+          <t>Palwal</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jhajjar</t>
+          <t>Panchkula</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bahadurgarh</t>
+          <t>Panchkula</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Jhajjar</t>
+          <t>Panchkula</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bahardurgarh</t>
+          <t>Pinjore</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Jhajjar</t>
+          <t>Panipat</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jhajjar</t>
+          <t>Panipat</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Jind</t>
+          <t>Rewari</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jind</t>
+          <t>Kosli</t>
         </is>
       </c>
     </row>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Jind</t>
+          <t>Rewari</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Narwana</t>
+          <t>Rewari</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kaithal</t>
+          <t>Rohtak</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kaithal</t>
+          <t>Rohtak</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Karnal</t>
+          <t>Sirsa</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Karnal</t>
+          <t>Sirsa</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kurukshetra</t>
+          <t>Sonipat</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kurukshetra</t>
+          <t>Gohana</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kurukshetra</t>
+          <t>Sonipat</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pehowa</t>
+          <t>Sonipat</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kurukshetra</t>
+          <t>Yamuna Nagar</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Shahabad-Markanda</t>
+          <t>Jagadhri</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mahendragarh</t>
+          <t>Yamuna Nagar</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Mahender Garh</t>
+          <t>Yamuna Nagar</t>
         </is>
       </c>
     </row>
@@ -2242,1117 +2242,1117 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Mahendragarh</t>
+          <t>Yamuna Nagar</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mahendergarh</t>
+          <t>Yamunanagar</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Mahendragarh</t>
+          <t>Bilaspur</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mahendergerh</t>
+          <t>Bilaspur</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mahendragarh</t>
+          <t>Hamirpur(HP)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Mahendragarh</t>
+          <t>Hamirpur</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Mahendragarh</t>
+          <t>Kangra</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mohinder Garh</t>
+          <t>Baijnath</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mahendragarh</t>
+          <t>Kangra</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Narnaul</t>
+          <t>Dharamshala</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Mahendragarh</t>
+          <t>Kangra</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Narnaul,</t>
+          <t>Jassur</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Mahendragarh</t>
+          <t>Kangra</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Narnoul</t>
+          <t>Kangra</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mahendragarh</t>
+          <t>Kangra</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Teh. Narnaul</t>
+          <t>Palampur</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Palwal</t>
+          <t>Kullu</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Palwal</t>
+          <t>Kullu</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Panchkula</t>
+          <t>Mandi</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Panchkula</t>
+          <t>Mandi</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Panchkula</t>
+          <t>Sirmaur</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Pinjore</t>
+          <t>Nahan</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Panipat</t>
+          <t>Solan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Panipat</t>
+          <t>Baddi</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Rewari</t>
+          <t>Solan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kosli</t>
+          <t>Nalagarh</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Rewari</t>
+          <t>Solan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Rewari</t>
+          <t>Solan</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Rohtak</t>
+          <t>Una</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Rohtak</t>
+          <t>Una</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Jammu and Kashmir</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sirsa</t>
+          <t>Jammu</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sirsa</t>
+          <t>Akhnoor</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Jammu and Kashmir</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sonipat</t>
+          <t>Jammu</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Gohana</t>
+          <t>Jammu</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Jammu and Kashmir</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sonipat</t>
+          <t>Kathua</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sonepat</t>
+          <t>Kathua</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Jammu and Kashmir</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sonipat</t>
+          <t>Kupwara</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sonepat Gohana</t>
+          <t>Kupwara</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Jammu and Kashmir</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Sonipat</t>
+          <t>Srinagar</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sonipat</t>
+          <t>Srinagar</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Yamuna Nagar</t>
+          <t>Dhanbad</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jagadhri</t>
+          <t>Dhanbad</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Yamuna Nagar</t>
+          <t>East Singhbhum</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Jagadhri (Hr)-135003</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Yamuna Nagar</t>
+          <t>Ranchi</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Yamuna Nagar</t>
+          <t>Ranchi</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Yamuna Nagar</t>
+          <t>Bagalkot</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Yamunanagar</t>
+          <t>Bagalkot</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bilaspur</t>
+          <t>Belagavi</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bilaspur</t>
+          <t>Belagavi</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Hamirpur(HP)</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hamirpur</t>
+          <t>Bangalore</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Kangra</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Baijnath</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Kangra</t>
+          <t>Dakshina Kannada</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Dharamshala</t>
+          <t>Mangalore</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Kangra</t>
+          <t>Davanagere</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jassur</t>
+          <t>Davanagere</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Kangra</t>
+          <t>Dharwad</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kangra</t>
+          <t>Dharwad</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Kangra</t>
+          <t>Dharwad</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Palampur</t>
+          <t>Hubballi</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kangra</t>
+          <t>Hassan</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Palmpur</t>
+          <t>Hassan</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Kullu</t>
+          <t>Kalaburagi</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Kullu</t>
+          <t>Kalaburagi</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Mandi</t>
+          <t>Kalaburagi</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mandi</t>
+          <t>Kalaburgi</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sirmaur</t>
+          <t>Kodagu</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Nahan</t>
+          <t>Ammathi</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Solan</t>
+          <t>Kodagu</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Baddi</t>
+          <t>Madikeri</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Solan</t>
+          <t>Kolar</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Nalagarh</t>
+          <t>Kolar</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Solan</t>
+          <t>Mysuru</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Solan</t>
+          <t>Mysuru</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Una</t>
+          <t>Shivamogga</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Una</t>
+          <t>Shimoga</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Jammu and Kashmir</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Jammu</t>
+          <t>Tumakuru</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Akhnoor</t>
+          <t>Tumkur</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Jammu and Kashmir</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Jammu</t>
+          <t>Udupi</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Jammu</t>
+          <t>Manipal</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Jammu and Kashmir</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Kathua</t>
+          <t>Vijayapura</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Kathua</t>
+          <t>Vijayapura</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Jammu and Kashmir</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Kupwara</t>
+          <t>Alappuzha</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Kupwara</t>
+          <t>Alappuzha</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Jammu and Kashmir</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Srinagar</t>
+          <t>Alappuzha</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Srinagar</t>
+          <t>Chengannur</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dhanbad</t>
+          <t>Alappuzha</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Dhanbad</t>
+          <t>Cherthala</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>East Singhbhum</t>
+          <t>Alappuzha</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Haripad</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ranchi</t>
+          <t>Alappuzha</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ranchi</t>
+          <t>Mavelikara</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Bagalkot</t>
+          <t>Ernakulam</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bagalkot</t>
+          <t>Cochin</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Belagavi</t>
+          <t>Ernakulam</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Belagavi</t>
+          <t>Ernakulam</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Ernakulam</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Kochi</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Ernakulam</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Thripunithura</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dakshina Kannada</t>
+          <t>Ernakulam</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Mangalore</t>
+          <t>Vazhakkala Village</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Davanagere</t>
+          <t>Idukki</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Davanagere</t>
+          <t>Kattappana</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dharwad</t>
+          <t>Idukki</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Dharwad</t>
+          <t>Thodupuzha</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Dharwad</t>
+          <t>Kannur</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Hubballi</t>
+          <t>Kannur</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Hassan</t>
+          <t>Kannur</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Hassan</t>
+          <t>Thalassery</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Kalaburagi</t>
+          <t>Kasaragod</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Kalaburagi</t>
+          <t>Kanhangad</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Kalaburagi</t>
+          <t>Kollam</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Kalaburgi</t>
+          <t>Kollam</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Kodagu</t>
+          <t>Kollam</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ammathi</t>
+          <t>Punalur</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Kodagu</t>
+          <t>Kottayam</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Madikeri</t>
+          <t>Changanacherry</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Kolar</t>
+          <t>Kottayam</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Kolar</t>
+          <t>Kottayam</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mysuru</t>
+          <t>Kozhikode</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Mysuru</t>
+          <t>Calicut</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Shivamogga</t>
+          <t>Kozhikode</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Shimoga</t>
+          <t>Kozhikode</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Tumakuru</t>
+          <t>Malappuram</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Tumkur</t>
+          <t>Malappuram</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Udupi</t>
+          <t>Malappuram</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Manipal</t>
+          <t>Manjeri</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Vijayapura</t>
+          <t>Malappuram</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Vijapur</t>
+          <t>Perintalmanna</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Alappuzha</t>
+          <t>Malappuram</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Alappuzha</t>
+          <t>Perinthalmanna</t>
         </is>
       </c>
     </row>
@@ -3381,12 +3381,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Alappuzha</t>
+          <t>Palakkad</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Chengannur</t>
+          <t>Mannarkkad</t>
         </is>
       </c>
     </row>
@@ -3398,12 +3398,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Alappuzha</t>
+          <t>Palakkad</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Cherthala</t>
+          <t>Ottapalam</t>
         </is>
       </c>
     </row>
@@ -3415,12 +3415,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Alappuzha</t>
+          <t>Palakkad</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Haripad</t>
+          <t>Palakkad</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Alappuzha</t>
+          <t>Pathanamthitta</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Mavelikara</t>
+          <t>Adoor</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Pathanamthitta</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Cochin</t>
+          <t>Kozhenchery</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Pathanamthitta</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Pathanamthitta</t>
         </is>
       </c>
     </row>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Pathanamthitta</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Thiruvalla</t>
         </is>
       </c>
     </row>
@@ -3500,12 +3500,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Thripunithura</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
     </row>
@@ -3517,12 +3517,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Thrissur</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Vazhakkala Village</t>
+          <t>Thrissur</t>
         </is>
       </c>
     </row>
@@ -3534,12 +3534,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Idukki</t>
+          <t>Wayanad</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Kattappana</t>
+          <t>Kalpetta</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Idukki</t>
+          <t>Wayanad</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Thodupuzha</t>
+          <t>Mananthavady</t>
         </is>
       </c>
     </row>
@@ -3568,675 +3568,675 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Kannur</t>
+          <t>Wayanad</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Kannur</t>
+          <t>Wayanad</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Kannur</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Thalassery</t>
+          <t>Bhopal</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Kasaragod</t>
+          <t>Burhanpur</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Kanahangad</t>
+          <t>Burhanpur</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Kollam</t>
+          <t>Dewas</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Kollam</t>
+          <t>Dewas</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Kollam</t>
+          <t>Gwalior</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Punalur</t>
+          <t>Gwalior</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Kottayam</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Changanacherry</t>
+          <t>Indore</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Kottayam</t>
+          <t>Jabalpur</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Kottayam</t>
+          <t>Jabalpur</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Kozhikode</t>
+          <t>Morena</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Morena</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Kozhikode</t>
+          <t>Rewa</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Kozhikode</t>
+          <t>Rewa</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Malappuram</t>
+          <t>Sagar</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Malappuram</t>
+          <t>Sagar</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Malappuram</t>
+          <t>Satna</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Manjeri</t>
+          <t>Chitrakoot</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Malappuram</t>
+          <t>Satna</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Perintalmanna</t>
+          <t>Satna</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Malappuram</t>
+          <t>Tikamgarh</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Printhalmanna</t>
+          <t>Tikamgarh</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Palakkad</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Mannarkkad</t>
+          <t>Ujjain</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Palakkad</t>
+          <t>Ahmed Nagar</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Ottapalam</t>
+          <t>Ahmednagar</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Palakkad</t>
+          <t>Ahmednagar</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Palakkad</t>
+          <t>Loni</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Pathanamthitta</t>
+          <t>Ahmednagar</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Adoor</t>
+          <t>Sangamner</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Pathanamthitta</t>
+          <t>Akola</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Kozhenchery</t>
+          <t>Akola</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Pathanamthitta</t>
+          <t>Amravati</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Pathanamthitta</t>
+          <t>Amravati</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Pathanamthitta</t>
+          <t>Aurangabad</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Thiruvalla</t>
+          <t>Aurangabad</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Beed</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Beed</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Buldhana</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Thiruvanthapuram</t>
+          <t>Buldhana</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Thrissur</t>
+          <t>Dhule</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Thrissur</t>
+          <t>Dhule</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Wayanad</t>
+          <t>Gondia</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Kalpetta</t>
+          <t>Gondia</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Wayanad</t>
+          <t>Jalgaon</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Mananthavady</t>
+          <t>Jalgaon</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Wayanad</t>
+          <t>Jalna</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Wayanad</t>
+          <t>Jalna</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Kolhapur</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Gadhinglaj</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Burhanpur</t>
+          <t>Kolhapur</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Burhanpur</t>
+          <t>Jaysingpur</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Dewas</t>
+          <t>Kolhapur</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Dewas</t>
+          <t>Kolhapur</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Gwalior</t>
+          <t>Latur</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Gwalior</t>
+          <t>Latur</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Chembur</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Jabalpur</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Jabalpur</t>
+          <t>Mumbai</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Morena</t>
+          <t>Mumbai Suburban</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Morena</t>
+          <t>West Mumbai Suburban</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Morena</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Morena (Nagar Nigm)</t>
+          <t>Kamptee</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Rewa</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Rewa</t>
+          <t>Nagpur</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Sagar</t>
+          <t>Nanded</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Sagar</t>
+          <t>Nanded</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Satna</t>
+          <t>Nashik</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Chitrakoot (Jankikund)</t>
+          <t>Nashik</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Satna</t>
+          <t>Osmanabad</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Satna</t>
+          <t>Omerga</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Tikamgarh</t>
+          <t>Osmanabad</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tikamgarh</t>
+          <t>Osmanabad</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Palghar</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Vasai</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4248,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Ahmed Nagar</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Ahmednagar</t>
+          <t>Baramati</t>
         </is>
       </c>
     </row>
@@ -4265,12 +4265,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Ahmednagar</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Loni</t>
+          <t>Bhosari</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Ahmednagar</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Sangamner</t>
+          <t>Pune</t>
         </is>
       </c>
     </row>
@@ -4299,12 +4299,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Akola</t>
+          <t>Ratnagiri</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Akola</t>
+          <t>Chiplun</t>
         </is>
       </c>
     </row>
@@ -4316,12 +4316,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Amravati</t>
+          <t>Ratnagiri</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Amravati</t>
+          <t>Ratnagiri</t>
         </is>
       </c>
     </row>
@@ -4333,12 +4333,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Aurangabad</t>
+          <t>Sangli</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Aurangabad</t>
+          <t>Miraj</t>
         </is>
       </c>
     </row>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Beed</t>
+          <t>Sangli</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Beed</t>
+          <t>Sangli</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Buldhana</t>
+          <t>Satara</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Buldhana</t>
+          <t>Bhiwadi</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Dhule</t>
+          <t>Satara</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Dhule</t>
+          <t>Karad</t>
         </is>
       </c>
     </row>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Gondia</t>
+          <t>Satara</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Gondia</t>
+          <t>Satara</t>
         </is>
       </c>
     </row>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Jalgaon</t>
+          <t>Sindhudurg</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Jalgaon</t>
+          <t>Kudal</t>
         </is>
       </c>
     </row>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Jalna</t>
+          <t>Solapur</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Jalna</t>
+          <t>Pandharpur</t>
         </is>
       </c>
     </row>
@@ -4452,12 +4452,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Kolhapur</t>
+          <t>Solapur</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Gadhinglaj</t>
+          <t>Solapur</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Kolhapur</t>
+          <t>Thane</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Jaysingpur</t>
+          <t>Bhiwandi</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Kolhapur</t>
+          <t>Thane</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Kolhapur</t>
+          <t>Dombivli</t>
         </is>
       </c>
     </row>
@@ -4503,12 +4503,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Latur</t>
+          <t>Thane</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Latur</t>
+          <t>Kalyan</t>
         </is>
       </c>
     </row>
@@ -4520,12 +4520,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Thane</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Chembur</t>
+          <t>Navi Mumbai</t>
         </is>
       </c>
     </row>
@@ -4537,12 +4537,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Thane</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Thane</t>
         </is>
       </c>
     </row>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Mumbai Suburban</t>
+          <t>Thane</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>West Mumbai Suburban</t>
+          <t>Thane West</t>
         </is>
       </c>
     </row>
@@ -4571,947 +4571,947 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Wardha</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Kamptee</t>
+          <t>Wardha</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Imphal West</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Imphal</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Meghalaya</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Nanded</t>
+          <t>East Khasi Hills</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Nanded</t>
+          <t>Shillong</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Nashik</t>
+          <t>Aizawl</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Nashik</t>
+          <t>Aizawl</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Osmanabad</t>
+          <t>Jhapa</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Omerga</t>
+          <t>Birtamode</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Osmanabad</t>
+          <t>Kaski</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Osmanabad</t>
+          <t>Kaski</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Palghar</t>
+          <t>Kaski</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Vasai (W)</t>
+          <t>Pokhara</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Baramati</t>
+          <t>Kathmandu</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Lalitpur</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Bhosari, Pune</t>
+          <t>Lalitpur</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Morang</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Biratnagar</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Ratnagiri</t>
+          <t>Palpa</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Chiplun</t>
+          <t>Tansen</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Ratnagiri</t>
+          <t>Rupandehi</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Ratnagiri</t>
+          <t>Butwal</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Sangli</t>
+          <t>Sunsari</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Miraj</t>
+          <t>Dharan</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Sangli</t>
+          <t>Baleswar</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Sangli</t>
+          <t>Balasore</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Satara</t>
+          <t>Bargarh</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bhiwadi</t>
+          <t>Bargarh</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Satara</t>
+          <t>Cuttack</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Karad</t>
+          <t>Cuttack</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Satara</t>
+          <t>Cuttack</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Satara</t>
+          <t>Madhupatna</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Sindhudurg</t>
+          <t>Dhenkanal</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Kudal</t>
+          <t>Dhenkanal</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Solapur</t>
+          <t>Ganjam</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Pandharpur</t>
+          <t>Berhampur</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Solapur</t>
+          <t>Ganjam</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Solapur</t>
+          <t>Bijipur</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Thane</t>
+          <t>Jajapur</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Bhiwandi</t>
+          <t>Jajpur</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Thane</t>
+          <t>Khorda</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Dombivli</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Thane</t>
+          <t>Khordha</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Kalyan (West), Thane</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Thane</t>
+          <t>Khordha</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Navi Mumbai</t>
+          <t>Khordha</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Thane</t>
+          <t>Puri</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Thane</t>
+          <t>Puri</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Thane</t>
+          <t>Sundergarh</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Thane West</t>
+          <t>Rourkela</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Wardha</t>
+          <t>Pondicherry</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Wardha</t>
+          <t>Pondicherry</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Imphal West</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Imphal</t>
+          <t>Madagadipet</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>East Khasi Hills</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Shillong</t>
+          <t>Puducherry</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Aizawl</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Aizawl</t>
+          <t>Amritsar</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Jhapa</t>
+          <t>Barnala</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Birtamode</t>
+          <t>Barnala</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Kaski</t>
+          <t>Bathinda</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Kaski</t>
+          <t>Bathinda</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Kaski</t>
+          <t>Bathinda</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Pokhara</t>
+          <t>Rampura Phul</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Faridkot</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Faridkot</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Lalitpur</t>
+          <t>Faridkot</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Lalitpur</t>
+          <t>Kotkapura</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Morang</t>
+          <t>Fatehgarh Sahib</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Biratnagar</t>
+          <t>Fatehgarh Sahib</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Palpa</t>
+          <t>Fatehgarh Sahib</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Tansen</t>
+          <t>Khamano</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Rupandehi</t>
+          <t>Fatehgarh Sahib</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Bitwal</t>
+          <t>Sirhind</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Rupandehi</t>
+          <t>Firozpur</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Butwal</t>
+          <t>Abohar</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Sunsari</t>
+          <t>Firozpur</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Dharan</t>
+          <t>Ferozepur</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Baleswar</t>
+          <t>Firozpur</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Balasore</t>
+          <t>Zira</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Bargarh</t>
+          <t>Gurdaspur</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Bargarh</t>
+          <t>Batala</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Cuttack</t>
+          <t>Gurdaspur</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Cuttack</t>
+          <t>Dinanagar</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Cuttack</t>
+          <t>Gurdaspur</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Opposite Madhupatna Ps</t>
+          <t>Gurdaspur</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Dhenkanal</t>
+          <t>Hoshiarpur</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Dhenkanal</t>
+          <t>Dasuya</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Ganjam</t>
+          <t>Hoshiarpur</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Berhampur</t>
+          <t>Hoshiarpur</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Ganjam</t>
+          <t>Hoshiarpur</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Bijipur</t>
+          <t>Mukerian</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Jajapur</t>
+          <t>Jalandhar</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Jajpur</t>
+          <t>Jalandhar</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Khorda</t>
+          <t>Kapurthala</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Kapurthala</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Khordha</t>
+          <t>Kapurthala</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Bhubaneshwar,</t>
+          <t>Lodhi</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Khordha</t>
+          <t>Kapurthala</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Khurdha, Bhubaneshwar</t>
+          <t>Phagwara</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Puri</t>
+          <t>Ludhiana</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Puri</t>
+          <t>Doraha</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Sundergarh</t>
+          <t>Ludhiana</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Rourkela</t>
+          <t>Jagraon</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Ludhiana</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Khanna</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Ludhiana</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Madagadipet</t>
+          <t>Ludhiana</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Mansa</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Bhikhi</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>Mansa</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>Budhlada</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Barnala</t>
+          <t>Mansa</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Barnala</t>
+          <t>Mansa</t>
         </is>
       </c>
     </row>
@@ -5557,12 +5557,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Bathinda</t>
+          <t>Moga</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Bathinda</t>
+          <t>Moga</t>
         </is>
       </c>
     </row>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Bathinda</t>
+          <t>Mohali</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Bhatinda</t>
+          <t>Kharar</t>
         </is>
       </c>
     </row>
@@ -5591,12 +5591,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Bathinda</t>
+          <t>Mohali</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Rampura Phul</t>
+          <t>Mohali</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Faridkot</t>
+          <t>Mohali</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Faridkot</t>
+          <t>Zirakpur</t>
         </is>
       </c>
     </row>
@@ -5625,12 +5625,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Faridkot</t>
+          <t>Muktsar</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Kotkapura</t>
+          <t>Muktsar</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Fatehgarh Sahib</t>
+          <t>Nawanshahr</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Fatehgarh Sahib</t>
+          <t>Banga</t>
         </is>
       </c>
     </row>
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Fatehgarh Sahib</t>
+          <t>Nawanshahr</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Khamano</t>
+          <t>Nawanshahr</t>
         </is>
       </c>
     </row>
@@ -5676,12 +5676,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Fatehgarh Sahib</t>
+          <t>Pathankot</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Sirhind</t>
+          <t>Pathankot</t>
         </is>
       </c>
     </row>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Firozpur</t>
+          <t>Patiala</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Patiala</t>
         </is>
       </c>
     </row>
@@ -5710,12 +5710,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Firozpur</t>
+          <t>Patiala</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Ferozepur</t>
+          <t>Rajpura</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Firozpur</t>
+          <t>Patiala</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Samana</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Gurdaspur</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Batala</t>
+          <t>Ropar</t>
         </is>
       </c>
     </row>
@@ -5761,12 +5761,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Gurdaspur</t>
+          <t>Rupnagar</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Dinanagar</t>
+          <t>Anandpur Sahib</t>
         </is>
       </c>
     </row>
@@ -5778,12 +5778,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Gurdaspur</t>
+          <t>Rupnagar</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Gurdaspur</t>
+          <t>Bhanupli</t>
         </is>
       </c>
     </row>
@@ -5795,12 +5795,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Hoshiarpur</t>
+          <t>Rupnagar</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Dasuya</t>
+          <t>Morinda</t>
         </is>
       </c>
     </row>
@@ -5812,12 +5812,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Hoshiarpur</t>
+          <t>Rupnagar</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Hoshiarpur</t>
+          <t>Nangal</t>
         </is>
       </c>
     </row>
@@ -5829,12 +5829,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Hoshiarpur</t>
+          <t>Rupnagar</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Mukerian</t>
+          <t>Nurpur Bedi</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Jalandhar</t>
+          <t>Rupnagar</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Jalandhar</t>
+          <t>Rupnagar</t>
         </is>
       </c>
     </row>
@@ -5863,12 +5863,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Kapurthala</t>
+          <t>Sangrur</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Kapurthala</t>
+          <t>Dhuri</t>
         </is>
       </c>
     </row>
@@ -5880,12 +5880,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Kapurthala</t>
+          <t>Sangrur</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Lodhi</t>
+          <t>Malerkotla</t>
         </is>
       </c>
     </row>
@@ -5897,12 +5897,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Kapurthala</t>
+          <t>Sangrur</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Phagwara</t>
+          <t>Sangrur</t>
         </is>
       </c>
     </row>
@@ -5914,12 +5914,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Ludhiana</t>
+          <t>Sangrur</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Doraha</t>
+          <t>Sunam</t>
         </is>
       </c>
     </row>
@@ -5931,12 +5931,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Ludhiana</t>
+          <t>Shahid Bhagat Singh Nagar</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>East Ludhiana</t>
+          <t>Nawanshahr</t>
         </is>
       </c>
     </row>
@@ -5948,12 +5948,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Ludhiana</t>
+          <t>Sri Muktsar Sahib</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Jagraon Ludhiana</t>
+          <t>Sri Muktsar Sahib</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Ludhiana</t>
+          <t>Tarn Taran</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Khanna</t>
+          <t>Bhikhiwind</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Ludhiana</t>
+          <t>Tarn Taran</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Ludhiana</t>
+          <t>Khalra</t>
         </is>
       </c>
     </row>
@@ -5999,556 +5999,556 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Mansa</t>
+          <t>Tarn Taran</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Bhikhi</t>
+          <t>Tarn Taran</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Mansa</t>
+          <t>Ajmer</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Budhlada</t>
+          <t>Ajmer</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Mansa</t>
+          <t>Ajmer</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Mansa</t>
+          <t>Kishangarh</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Moga</t>
+          <t>Alwar</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Moga</t>
+          <t>Alwar</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Mohali</t>
+          <t>Barmer</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Kharar</t>
+          <t>Barmer</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Mohali</t>
+          <t>Bharatpur</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Mohali</t>
+          <t>Bharatpur</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Mohali</t>
+          <t>Bharatpur</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Zirakpur</t>
+          <t>Nadbai</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Muktsar</t>
+          <t>Bhilwara</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Muktsar</t>
+          <t>Bhilwara</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Nawanshahr</t>
+          <t>Bikaner</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Bikaner</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Nawanshahr</t>
+          <t>Churu</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Nawanshahr</t>
+          <t>Churu</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Pathankot</t>
+          <t>Churu</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Pathankot</t>
+          <t>Rajgarh Churu</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Patiala</t>
+          <t>Dausa</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Dist Patiala</t>
+          <t>Dausa</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Patiala</t>
+          <t>Didwana-Kuchaman</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Patiala</t>
+          <t>Didwana</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Patiala</t>
+          <t>Ganganagar</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Rajpura</t>
+          <t>Sriganganagar</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Patiala</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Samana</t>
+          <t>Chomu</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Jaipur</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Rupnagar</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Anandpur Sahib</t>
+          <t>Kotputli</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Rupnagar</t>
+          <t>Jhujhunu</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Bhanupli</t>
+          <t>Buhana</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Rupnagar</t>
+          <t>Jhujhunu</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Morind</t>
+          <t>Chirawa</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Rupnagar</t>
+          <t>Jhujhunu</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Nangal</t>
+          <t>Jhunjhunu</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Rupnagar</t>
+          <t>Jhujhunu</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Nurpur Bedi</t>
+          <t>Pilani</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Rupnagar</t>
+          <t>Jodhpur</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Rupnagar</t>
+          <t>Jodhpur</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Rupnagar</t>
+          <t>Kota</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Sri Anandpur Sahib</t>
+          <t>Kota</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Sangrur</t>
+          <t>Kotputli-Behror</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Dhuri</t>
+          <t>Behror</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Sangrur</t>
+          <t>Nagaur</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Malerkotla</t>
+          <t>Kuchaman City</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Sangrur</t>
+          <t>Nagaur</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Sangrur</t>
+          <t>Nagaur</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Sangrur</t>
+          <t>Neem Ka Thana</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Sunam</t>
+          <t>Neem Ka Thana</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Shahid Bhagat Singh Nagar</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Nawanshar</t>
+          <t>Pali</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Shahid Bhagat Singh Nagar</t>
+          <t>Rajsamand</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Sbs Nagar</t>
+          <t>Rajsamand</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Sri Muktsar Sahib</t>
+          <t>Sawai Madhopur</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Sri Muktsar Sahib</t>
+          <t>Sawaimadhopur</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Tarn Taran</t>
+          <t>Sikar</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Bhikhiwind</t>
+          <t>Fatehpur</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Tarn Taran</t>
+          <t>Sikar</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Khalra</t>
+          <t>Reengus</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Tarn Taran</t>
+          <t>Sikar</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Tarn Taran</t>
+          <t>Sikar</t>
         </is>
       </c>
     </row>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Ajmer</t>
+          <t>Sirohi</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Ajmer</t>
+          <t>Mount Abu</t>
         </is>
       </c>
     </row>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Ajmer</t>
+          <t>Sri Ganganagar</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Madanganj -Kishangarh</t>
+          <t>Sri Ganganagar</t>
         </is>
       </c>
     </row>
@@ -6594,12 +6594,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Alwar</t>
+          <t>Sri Ganganagar</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Alwar</t>
+          <t>Suratgarh</t>
         </is>
       </c>
     </row>
@@ -6611,1270 +6611,1270 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Barmer</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Barmer</t>
+          <t>Udaipur</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Bharatpur</t>
+          <t>East Sikkim</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Bharatpur</t>
+          <t>Gangtok</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Bharatpur</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Nadbi</t>
+          <t>Chennai</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Bhilwara</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Bhilwara</t>
+          <t>Coimbatore</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Bikaner</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Bikaner</t>
+          <t>Tirupur</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Churu</t>
+          <t>Dindigul</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Churu</t>
+          <t>Dindigul</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Churu</t>
+          <t>Erode</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Rajgarh Churu</t>
+          <t>Erode</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Dausa</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Dausa</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Didwana-Kuchaman</t>
+          <t>Kanyakumari</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Didwana</t>
+          <t>Kanniyakumari</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Ganganagar</t>
+          <t>Kanyakumari</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Sriganganagar</t>
+          <t>Kulasekharam</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Kanyakumari</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Chomu</t>
+          <t>Marthandam</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Kanyakumari</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Nagercoil</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Karur</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Kotputli</t>
+          <t>Karur</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Jhujhunu</t>
+          <t>Krishnagiri</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Buhana</t>
+          <t>Krishnagiri</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Jhujhunu</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Chirawa</t>
+          <t>Madurai</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Jhujhunu</t>
+          <t>Namakkal</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Jhunjhunu</t>
+          <t>Namakkal</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Jhujhunu</t>
+          <t>Salem</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Pilani</t>
+          <t>Salem</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Jodhpur</t>
+          <t>Sivaganga</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Jodhpur</t>
+          <t>Karaikudi</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Kota</t>
+          <t>Thanjavur</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Kota</t>
+          <t>Kumbakonam</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Kotputli-Behror</t>
+          <t>Thanjavur</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Behror</t>
+          <t>Thanjavur</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Nagaur</t>
+          <t>Theni</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Kuchanam City</t>
+          <t>Theni</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Nagaur</t>
+          <t>Thoothukudi</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Nagaur</t>
+          <t>Kovilpatti</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Neem Ka Thana</t>
+          <t>Tiruchirappalli</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Neem Ka Thana</t>
+          <t>Tiruchirappalli</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Tirunelveli</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Kokkirakulam</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Rajsamand</t>
+          <t>Tirunelveli</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Rajsamand</t>
+          <t>Tirunelveli</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Sawai Madhopur</t>
+          <t>Tiruvannamalai</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Sawaimadhopur</t>
+          <t>Tiruvannamalai</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Sikar</t>
+          <t>Tiruvarur</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Fatehpur</t>
+          <t>Tiruvarur</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Sikar</t>
+          <t>Tuticorin</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Reengus</t>
+          <t>Tuticorin</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Sikar</t>
+          <t>Vellore</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Sikar</t>
+          <t>Ranipet</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Sirohi</t>
+          <t>Vellore</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Mount Abu</t>
+          <t>Vellore</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Sri Ganganagar</t>
+          <t>Virudhunagar</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Sri Ganganagar</t>
+          <t>Rajapalayam</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Sri Ganganagar</t>
+          <t>Virudhunagar</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Suratgarh</t>
+          <t>Sivakasi</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Virudhunagar</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Srivilliputhur</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>East Sikkim</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Gangtok</t>
+          <t>Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Secunderabad</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Karim Nagar</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Karimnagar</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Khammam</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Tirupur</t>
+          <t>Khammam</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Dindigul</t>
+          <t>Mahabubnagar</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Dindigul</t>
+          <t>Mahabubnagar</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Erode</t>
+          <t>Warangal</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Erode</t>
+          <t>Warangal</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>West Tripura</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Agartala</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Kanyakumari</t>
+          <t>Agra</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Kanniyakumari</t>
+          <t>Agra</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Kanyakumari</t>
+          <t>Aligarh</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Kulasekharam</t>
+          <t>Aligarh</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Kanyakumari</t>
+          <t>Allahabad</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Marthandam</t>
+          <t>Allahabad</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Kanyakumari</t>
+          <t>Ayodhya</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Nagercoil</t>
+          <t>Ayodhya</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Karur</t>
+          <t>Azamgarh</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Karur</t>
+          <t>Azamgarh</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Krishnagiri</t>
+          <t>Baghpat</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Krishnagiri</t>
+          <t>Baraut</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Bagpat</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Baghpat</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Namakkal</t>
+          <t>Ballia</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Namakkal</t>
+          <t>Ballia</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Salem</t>
+          <t>Bareilly</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Salem</t>
+          <t>Bareilly</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Sivaganga</t>
+          <t>Bhadohi</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Karaikudi</t>
+          <t>Bhadohi</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Thanjavur</t>
+          <t>Bijnor</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Kumbakonam</t>
+          <t>Bijnor</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Thanjavur</t>
+          <t>Bulandshahr</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Thanjavur</t>
+          <t>Bulandshahr</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Theni</t>
+          <t>Bulandshahr</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Theni</t>
+          <t>Sikandrabad</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Thoothukudi</t>
+          <t>Etawah</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Kovitpatti</t>
+          <t>Etawah</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Tiruchirappalli</t>
+          <t>Farrukhabad</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Tiruchirapalli</t>
+          <t>Farrukhabad</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Tiruchirappalli</t>
+          <t>Firozabad</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Tiruchirappalli</t>
+          <t>Firozabad</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Tiruchirappalli</t>
+          <t>Gautam Buddha Nagar</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Trichirapalli</t>
+          <t>Gautam Buddha Nagar</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Tiruchirappalli</t>
+          <t>Gautam Buddha Nagar</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Trichy</t>
+          <t>Greater Noida</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Tirunelveli</t>
+          <t>Gautam Buddha Nagar</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Kokkirakulam</t>
+          <t>Jewar</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Tirunelveli</t>
+          <t>Gautam Buddha Nagar</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Tirunelveli</t>
+          <t>Noida</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Tiruvannamalai</t>
+          <t>Ghaziabad</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Tiruvannamalai</t>
+          <t>Ghaziabad</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Tiruvarur</t>
+          <t>Ghaziabad</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Tiruvarur</t>
+          <t>Sahibabad</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Tuticorin</t>
+          <t>Gorakhpur</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Tuticorin</t>
+          <t>Gorakhpur</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Vellore</t>
+          <t>Hapur</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Ranipet</t>
+          <t>Hapur</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Vellore</t>
+          <t>Jalaun</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Vellore</t>
+          <t>Orai</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Virudhunagar</t>
+          <t>Jaunpur</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Rajapalayam</t>
+          <t>Jaunpur</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Virudhunagar</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Sivakasi</t>
+          <t>Jhansi</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Virudhunagar</t>
+          <t>Kanpur Nagar</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Srivilliputhur</t>
+          <t>Kanpur</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Kanpur Nagar</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Kanpur Nagar</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Secunderabad</t>
+          <t>Lucknow</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Karim Nagar</t>
+          <t>Maharajganj</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Karimnagar</t>
+          <t>Maharajganj</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Khammam</t>
+          <t>Mathura</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Khammam</t>
+          <t>Mathura</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Mahabubnagar</t>
+          <t>Mau</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Mahbubnagar</t>
+          <t>Mau</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Warangal</t>
+          <t>Meerut</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Warangal</t>
+          <t>Meerut</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>West Tripura</t>
+          <t>Mirzapur</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Agartala</t>
+          <t>Mirzapur</t>
         </is>
       </c>
     </row>
@@ -7886,12 +7886,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Agra</t>
+          <t>Moradabad</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Agra</t>
+          <t>Moradabad</t>
         </is>
       </c>
     </row>
@@ -7903,12 +7903,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Aligarh</t>
+          <t>Muzaffarnagar</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Aligarh</t>
+          <t>Muzaffarnagar</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Allahabad</t>
+          <t>Pilibhit</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Allahabad</t>
+          <t>Pilibhit</t>
         </is>
       </c>
     </row>
@@ -7937,12 +7937,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Ayodhya</t>
+          <t>Pratapgarh</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Ayodhya</t>
+          <t>Pratapgarh</t>
         </is>
       </c>
     </row>
@@ -7954,12 +7954,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Azamgarh</t>
+          <t>Prayagraj</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Azamgarh</t>
+          <t>Prayagraj</t>
         </is>
       </c>
     </row>
@@ -7971,12 +7971,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Baghpat</t>
+          <t>Raebareli</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Baraut (Baghpat)</t>
+          <t>Raebareli</t>
         </is>
       </c>
     </row>
@@ -7988,12 +7988,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Bagpat</t>
+          <t>Rampur</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Baghpat</t>
+          <t>Rampur</t>
         </is>
       </c>
     </row>
@@ -8005,12 +8005,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Ballia</t>
+          <t>Saharanpur</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Balia</t>
+          <t>Saharanpur</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Ballia</t>
+          <t>Shahjahanpur</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Ballia</t>
+          <t>Shahjahanpur</t>
         </is>
       </c>
     </row>
@@ -8039,1166 +8039,435 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Bareilly</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Bareilly</t>
+          <t>Varanasi</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Bhadohi</t>
+          <t>Almora</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Bhadohi</t>
+          <t>Almora</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Bijnor</t>
+          <t>Dehradun</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Bijnor</t>
+          <t>Dehradun</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Bulandshahr</t>
+          <t>Dehradun</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Bulandshahr</t>
+          <t>Rishikesh</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Bulandshahr</t>
+          <t>Dehradun</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Sikandrabad</t>
+          <t>Rudrapur</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Bulandshahr</t>
+          <t>Haridwar</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Sikandrabad, Bulandshahr</t>
+          <t>Haridwar</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Etawah</t>
+          <t>Haridwar</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Etawah</t>
+          <t>Roorkee</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Farrukhabad</t>
+          <t>Nainital</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Farrukhabad</t>
+          <t>Haldwani</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Firozabad</t>
+          <t>Nainital</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Firozabad</t>
+          <t>Nainital</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Gautam Buddha Nagar</t>
+          <t>Nainital</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>G B Nagar</t>
+          <t>Ramnagar</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Gautam Buddha Nagar</t>
+          <t>Pauri Garhwal</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Gautam Buddha Nagar</t>
+          <t>Kotdwar</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Gautam Buddha Nagar</t>
+          <t>Pauri Garhwal</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Greater Noida</t>
+          <t>Pauri</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Gautam Buddha Nagar</t>
+          <t>Udham Singh Nagar</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Greater Noida (West)</t>
+          <t>Kashipur</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Gautam Buddha Nagar</t>
+          <t>Udham Singh Nagar</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Jewar</t>
+          <t>Khatima</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Gautam Buddha Nagar</t>
+          <t>Udham Singh Nagar</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Noida</t>
+          <t>Udham Singh Nagar</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Ghaziabad</t>
+          <t>Bankura</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Ghaziabad</t>
+          <t>Bankura</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Ghaziabad</t>
+          <t>Birbhum</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Sahidabad</t>
+          <t>Bolpur</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Gorakhpur</t>
+          <t>Darjiling</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Gorakhpur</t>
+          <t>Siliguri</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Hapur</t>
+          <t>Hooghly</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>District - Hapur</t>
+          <t>Hooghly</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Hapur</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Hapur</t>
+          <t>Baghajatin</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Jalaun</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Orai</t>
+          <t>Kolkata</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Jaunpur</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Jaunpur</t>
+          <t>Kalyani</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>North 24 Parganas</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>Barasat</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Kanpur Nagar</t>
+          <t>North Dinajpur</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Raiganj</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Kanpur Nagar</t>
+          <t>Paschim Bardhaman</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Kanpur Nagar</t>
+          <t>Durgapur</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Purba Bardhaman</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
-        <is>
-          <t>Lucknow</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>Maharajganj</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>Maharajganj</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>Mathura</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>Mathura</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>Mau</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>Mau</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>Meerut</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>Meerut</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>Mirzapur</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>Mirzapur</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>Moradabad</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>Moradabad</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>Muzaffarnagar</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>Muzaffarnagar</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>Pilibhit</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>Pilibhit</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>Pratapgarh</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>Pratapgarh</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>Prayagraj</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>Prayagraj</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>Prayagraj</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>Prayagraj (Allahabad)</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>Raebareli</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>Raebareli</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>Rampur</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>Rampur</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>Saharanpur</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>Saharanpur</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>Shahjahanpur</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>Shahjahanpur</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>Varanasi</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>Varanasi</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>Almora</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>Almora</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>Dehradun</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>Dehradun</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>Dehradun</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>Rishikesh</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>Dehradun</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>Rudrapur</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>Haridwar</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>Haridwar</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>Haridwar</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>Roorkee</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>Nainital</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>Haldwani</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>Nainital</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>Haldwani (Nainital)</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>Nainital</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>Haldwani,Nainital</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>Nainital</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>Nainital</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>Nainital</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>Ram Nagar</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>Pauri Garhwal</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>Kotdwar</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>Pauri Garhwal</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>Pauri</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>Udham Singh Nagar</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>Dist U S Nagar</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>Udham Singh Nagar</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>Kashipur</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>Uttarakhand</t>
-        </is>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>Udham Singh Nagar</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>Khatima</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>Bankura</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>Bankura</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>Birbhum</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>Bolpur</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>Darjiling</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>Siliguri</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>Hooghly</t>
-        </is>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>Hooghly</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>Kolkata</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>Baghajatin</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>Kolkata</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>Kolkata</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>Nadia</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>Kalyani</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>North 24 Parganas</t>
-        </is>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>Barasat</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>North Dinajpur</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>Raiganj</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>Paschim Bardhaman</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>Durgapur</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>Purba Bardhaman</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
         <is>
           <t>Bardhaman</t>
         </is>
